--- a/data/CLEAN_country_year_panel_2010-2022.xlsx
+++ b/data/CLEAN_country_year_panel_2010-2022.xlsx
@@ -15514,10 +15514,10 @@
       <c r="L207" t="n">
         <v>19.665</v>
       </c>
-      <c r="O207" t="n">
+      <c r="S207" t="n">
         <v>30100</v>
       </c>
-      <c r="P207" t="n">
+      <c r="T207" t="n">
         <v>0.327</v>
       </c>
       <c r="X207" t="inlineStr">
@@ -15530,7 +15530,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AA207" t="inlineStr">
+      <c r="AB207" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -37952,10 +37952,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C6" t="n">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
         <v>12</v>
@@ -37978,13 +37978,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C7" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -37993,7 +37993,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AUT, BEL, BGR, CHE, CHL, CHN, CZE, DEU, DNK, ESP, FIN, FRA, GBR, HRV, HUN, IND, ISL, ISR, ITA, LTU, MEX, NLD, NOR, PHL, POL, PRT, RUS, SUR, SVK, SVN, SWE, THA, TUR, USA, ZAF</t>
+          <t>AUT, BEL, BGR, CHE, CHL, CHN, CZE, DEU, DNK, ESP, FIN, FRA, GBR, HRV, HUN, IND, ISL, ITA, LTU, MEX, NLD, NOR, PHL, POL, PRT, RUS, SUR, SVK, SVN, SWE, THA, TUR, USA, ZAF</t>
         </is>
       </c>
     </row>

--- a/data/CLEAN_country_year_panel_2010-2022.xlsx
+++ b/data/CLEAN_country_year_panel_2010-2022.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Country_year" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codebook" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revision_history" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -498,7 +499,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Compiled and verified 2026-08-17; Eurostat migr_eipre re-verified 2026-08-18.</t>
+          <t>Sources first retrieved and verified 2026-08-17. Data last revised 2026-10-02. Every amendment since is dated on the Revision_history sheet.</t>
         </is>
       </c>
     </row>
@@ -38052,4 +38053,709 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="29" customWidth="1" min="6" max="6"/>
+    <col width="64" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="72" customWidth="1" min="13" max="13"/>
+    <col width="72" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>amends_data</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>iso3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>scope_zh</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>before</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>before_zh</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>after</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>after_zh</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>change</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>change_zh</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>187428a</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>first publication</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>All 40 countries</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>全部 40 國</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2,219 values</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2,219 筆數值</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Archive first published. Sources had been retrieved and every value compared with them earlier the same day; 49 values that disagreed with their source were corrected before publication and are itemised in Corrections applied.</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>本存檔首次發布。同日稍早已重新取得各資料來源並逐筆比對；與來源不符之 49 筆數值已於發布前更正，逐筆列於「已套用之更正」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>21:13</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>812502d</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>value corrected</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>KOR</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Korea · overstayers · 2015</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>南韓 · 逾期停留 · 2015</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>212,596</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>212,596</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>214,168</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>214,168</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>The input figure was a 31 August snapshot inside a year-end series. Replaced with the year-end value from the Ministry of Justice yearbook, and 2010-2015 re-cited to that official series in place of a secondary source whose host no longer responds. 2010-2014 values unchanged; grades raised from D to A and B.</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>原始數值為年底序列中的 8 月 31 日快照，改以法務部統計年報之年底數值取代；並將 2010–2015 年改引該官方序列，取代主機已無回應之次級來源。2010–2014 年數值不變；等級自 D 提升為 A 與 B。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>22:19</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>23b57c4</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>value deleted</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>RUS</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Russia · irregular stock · 2020</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>俄羅斯 · 無證移民存量 · 2020</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1,200,000</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1,200,000</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>deleted</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>已刪除</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>The cited source, as archived, contains no numeric estimate. Removed under the rule that a value which cannot be traced to its source is not published.</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>所引用之來源於存檔版本中並無任何數值推估。依「無法追溯至來源之數值不予發布」之原則刪除。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>22:19</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>23b57c4</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>flagged as derived</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>AUT;CHE;CZE;DEU;FRA;GBR;NLD</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Irregular stock · 13 cells</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>無證移民存量 · 13 格</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>unmarked</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>未標示</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>marked as derived, grade C</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>標示為推導值，C 級</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Values unchanged. Each is the midpoint of a range Pew Research published, not a figure Pew published; now marked as derived, graded C, and shown beside the range.</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>數值不變。各值為 Pew Research 所公布區間之中點，而非其公布之數字；現標示為推導值、評為 C 級，並與原區間並列呈現。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0d54c7d</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>re-verified</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Eurostat migr_eipre · 283 values</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Eurostat migr_eipre · 283 筆數值</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>86.2% reproduced</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>重現率 86.2%</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>100% reproduced</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>重現率 100%</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Values unchanged by this step. Every detection value re-queried live and compared with the corrected panel; all 283 matched. The 86.2% first result reflected the input workbook's one-year offset, corrected before publication.</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>此步驟未變更數值。所有查獲人次數值皆即時重新查詢，並與更正後之 panel 比對，283 筆全數一致。首次測試之 86.2% 係反映原始工作表之一年位移，該位移已於發布前更正。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>f9d7ae3</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>source re-cited</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CHE;ITA;JPN;KOR</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Switzerland 2015; Italy 2019-2022; Japan 2014; Korea 2010-2015</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>瑞士 2015；義大利 2019–2022；日本 2014；南韓 2010–2015</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>dead or blocked URLs cited</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>引用已失效或遭封鎖之網址</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>live source cited</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>改引仍可取得之來源</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Values unchanged. Where the citation supplied with the data had gone dead, the value is now cited to a live document stating the same figure, and the original is kept as a superseded citation. Italy 2022 moved to the XXVIII Rapporto, because the ISMU series ends at 2021.</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>數值不變。原引用來源已失效者，改引仍可取得且載有相同數字之文件，原引用則保留為已更替之引用來源。義大利 2022 年改引第 XXVIII 號報告，因 ISMU 序列止於 2021 年。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>34707a5</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>evidence added</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>CHE;ITA;KOR</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Switzerland, Italy, Korea</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>瑞士、義大利、南韓</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>5 snapshots, 2 documents</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>5 份快照、2 份文件</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Values unchanged. Dated live snapshots captured of the re-cited sources, and the two ISMU press releases originally cited were retrieved and archived; both state the published figures. The claim that ismu.org refused every client was corrected.</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>數值不變。已擷取改引來源之日期戳記即時快照，並取得、存檔原引用之兩份 ISMU 新聞稿，其內容均載有所公布之數字。已更正「ismu.org 拒絕所有用戶端」之敘述。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>d50724c</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>value reclassified</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ISR</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Israel · 2020</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>以色列 · 2020</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>irregular stock 30,100</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>無證移民存量 30,100</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>overstayers 30,100</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>逾期停留 30,100</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>The 2020 and 2022 cells of irregular stock counted two mutually exclusive populations: tourists who overstayed, and infiltrators via the Egyptian border. The 2020 figure is an overstay count, so it now sits under overstayers, credited to the Central Bureau of Statistics as the source states.</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>無證移民存量 2020 與 2022 年兩格所計為互不重疊之兩種人口：逾期停留之觀光客，以及自埃及邊界非法入境者。2020 年數值屬逾期停留數，現改列於逾期停留欄位，並依來源所載註明出處為中央統計局。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>d50724c</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>note amended</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ISR</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Israel · irregular stock · 2022</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>以色列 · 無證移民存量 · 2022</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>26,798</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>26,798</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>26,798 (lower bound)</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>26,798（下限）</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Value unchanged. The note now states that it counts infiltrators only and so understates the unauthorised population, which on that date was at least 49,369.</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>數值不變。備註現已載明其僅計入非法入境者，故低估未經許可人口；該日之未經許可人口至少為 49,369。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/CLEAN_country_year_panel_2010-2022.xlsx
+++ b/data/CLEAN_country_year_panel_2010-2022.xlsx
@@ -66146,7 +66146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -66157,7 +66157,7 @@
     <col width="72" customWidth="1" min="6" max="6"/>
     <col width="72" customWidth="1" min="7" max="7"/>
     <col width="54" customWidth="1" min="8" max="8"/>
-    <col width="33" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="39" customWidth="1" min="11" max="11"/>
     <col width="30" customWidth="1" min="12" max="12"/>
@@ -66846,6 +66846,16 @@
           <t>2026-10-07</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>02:48</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>529dab6</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>range extended</t>
@@ -66908,6 +66918,16 @@
           <t>2026-10-07</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>02:48</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>529dab6</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>re-verified</t>
@@ -66960,6 +66980,16 @@
           <t>2026-10-07</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>02:48</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>529dab6</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>note amended</t>
@@ -67022,6 +67052,16 @@
           <t>2026-10-07</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>02:48</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>529dab6</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>collection attempted, not obtained</t>
@@ -67060,6 +67100,58 @@
       <c r="N14" t="inlineStr">
         <is>
           <t>澳洲：澳洲統計局普查 QuickStats 頁面不含公民身分總數，另一個澳洲統計局主機無法解析，故未取得全國非公民人數。智利：INE 2017 年普查綜合報告載有 2017 年數（746,465），但 2002 年僅有比例（1.27%）；可能載有 2002 年人數之較長報告於下載途中中斷，且不從百分比推算人數。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>manifest corrected</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>manifest/checksums.csv · text files and 24 raw captures</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>manifest/checksums.csv · 文字檔與 24 個原始擷取檔</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>hashes of the Windows working copy</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>依 Windows 工作資料夾計算之雜湊值</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>hashes of the bytes the site serves</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>依網站實際提供之位元組計算之雜湊值</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Values unchanged. The checksum manifest had been built from the working folder, where git on Windows writes text files with CRLF line endings, while GitHub serves them with LF; the hash of any downloaded CSV, page or Markdown file therefore differed from the recorded one (PDF, image and spreadsheet files were not affected). The manifest now hashes the bytes the site serves, scripts/78_verify_checksums.py checks every row against what git stored, and 24 downloaded web pages and CSV files whose servers send CRLF are now stored byte for byte as saved (.gitattributes) instead of with the line endings converted.</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>數值不變。雜湊清單原是依工作資料夾計算；在 Windows 上，git 於工作資料夾以 CRLF 寫入文字檔，而 GitHub 提供之檔案為 LF，故任何下載之 CSV、網頁或 Markdown 檔之雜湊值皆與記錄不符（PDF、圖片與試算表檔不受影響）。現清單改依網站實際提供之位元組計算，並以 scripts/78_verify_checksums.py 將每一列與 git 所存內容核對；另有 24 個下載之網頁與 CSV 檔（其伺服器以 CRLF 傳送）現已逐位元組依所存內容保存（.gitattributes），不再轉換換行字元。</t>
         </is>
       </c>
     </row>

--- a/data/CLEAN_country_year_panel_2010-2022.xlsx
+++ b/data/CLEAN_country_year_panel_2010-2022.xlsx
@@ -67075,6 +67075,16 @@
           <t>2026-10-07</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1b845d0</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>value corrected</t>
@@ -67137,6 +67147,16 @@
           <t>2026-10-07</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1b845d0</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>value corrected</t>
@@ -67199,6 +67219,16 @@
           <t>2026-10-07</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1b845d0</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>value corrected</t>
@@ -67261,6 +67291,16 @@
           <t>2026-10-07</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1b845d0</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>value corrected</t>
@@ -67323,6 +67363,16 @@
           <t>2026-10-07</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1b845d0</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>value corrected</t>
@@ -67385,6 +67435,16 @@
           <t>2026-10-07</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1b845d0</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>value deleted</t>
@@ -67447,6 +67507,16 @@
           <t>2026-10-07</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1b845d0</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>source re-cited</t>
@@ -67509,6 +67579,16 @@
           <t>2026-10-07</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1b845d0</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>values added</t>
@@ -67571,6 +67651,16 @@
           <t>2026-10-07</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1b845d0</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>grade changed</t>
@@ -67633,6 +67723,16 @@
           <t>2026-10-07</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1b845d0</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>flag changed</t>
@@ -67695,6 +67795,16 @@
           <t>2026-10-07</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1b845d0</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>value reclassified</t>
@@ -67757,6 +67867,16 @@
           <t>2026-10-07</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1b845d0</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>evidence added</t>
@@ -67802,6 +67922,16 @@
       <c r="A27" t="inlineStr">
         <is>
           <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1b845d0</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">

--- a/data/CLEAN_country_year_panel_2010-2022.xlsx
+++ b/data/CLEAN_country_year_panel_2010-2022.xlsx
@@ -68029,6 +68029,16 @@
           <t>2026-10-07</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>21:18</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>f093c3e</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>flagged as derived</t>
@@ -68091,6 +68101,16 @@
           <t>2026-10-07</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>21:18</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>f093c3e</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>flag changed</t>
@@ -68153,6 +68173,16 @@
           <t>2026-10-07</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>21:18</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>f093c3e</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>re-verified</t>
@@ -68203,6 +68233,16 @@
       <c r="A31" t="inlineStr">
         <is>
           <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>21:18</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>f093c3e</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">

--- a/data/CLEAN_country_year_panel_2010-2022.xlsx
+++ b/data/CLEAN_country_year_panel_2010-2022.xlsx
@@ -75547,6 +75547,16 @@
           <t>2026-10-17</t>
         </is>
       </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>21:52</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>d05a8d6</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
           <t>variable added</t>
@@ -75607,6 +75617,16 @@
       <c r="A34" t="inlineStr">
         <is>
           <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>21:52</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>d05a8d6</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">

--- a/data/CLEAN_country_year_panel_2010-2022.xlsx
+++ b/data/CLEAN_country_year_panel_2010-2022.xlsx
@@ -75791,6 +75791,16 @@
           <t>2026-10-18</t>
         </is>
       </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>cedba02</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
           <t>note amended</t>
@@ -75853,6 +75863,16 @@
           <t>2026-10-18</t>
         </is>
       </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>cedba02</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
           <t>documentation corrected</t>
@@ -75905,6 +75925,16 @@
           <t>2026-10-18</t>
         </is>
       </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>cedba02</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
           <t>values added</t>
@@ -75967,6 +75997,16 @@
           <t>2026-10-18</t>
         </is>
       </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>cedba02</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
           <t>documentation corrected</t>
@@ -76017,6 +76057,16 @@
       <c r="A39" t="inlineStr">
         <is>
           <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>cedba02</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">

--- a/data/CLEAN_country_year_panel_2010-2022.xlsx
+++ b/data/CLEAN_country_year_panel_2010-2022.xlsx
@@ -83589,6 +83589,16 @@
           <t>2026-10-21</t>
         </is>
       </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>4b161c9</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
           <t>variable added</t>
@@ -83651,6 +83661,16 @@
           <t>2026-10-21</t>
         </is>
       </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>4b161c9</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
           <t>documentation corrected</t>
@@ -83701,6 +83721,16 @@
       <c r="A42" t="inlineStr">
         <is>
           <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>4b161c9</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">

--- a/data/CLEAN_country_year_panel_2010-2022.xlsx
+++ b/data/CLEAN_country_year_panel_2010-2022.xlsx
@@ -90929,6 +90929,16 @@
           <t>2026-10-26</t>
         </is>
       </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ea42395</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
           <t>variable added</t>

--- a/data/CLEAN_country_year_panel_2010-2022.xlsx
+++ b/data/CLEAN_country_year_panel_2010-2022.xlsx
@@ -97251,6 +97251,16 @@
           <t>2026-10-29</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>21:33</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>8fd6c7f</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
           <t>variable added</t>

--- a/data/CLEAN_country_year_panel_2010-2022.xlsx
+++ b/data/CLEAN_country_year_panel_2010-2022.xlsx
@@ -967,7 +967,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Survey years only (679 of 880 country-years); do not interpolate without saying so. Consumption-based values (flagged) are lower than income-based ones; flagged breaks mark a change of survey; New Zealand is from the OECD on a different income concept (flagged). The World Bank revises past values with new releases; the values are those published when retrieved (2026-10-29).</t>
+          <t>Survey years only (679 of 880 country-years); do not interpolate without saying so. Consumption-based values (flagged) measure a different concept from income-based ones (often, but not always, lower); flagged breaks mark a change of survey; New Zealand is from the OECD on a different income concept (flagged). The World Bank revises past values with new releases; the values are those published when retrieved (2026-10-29).</t>
         </is>
       </c>
     </row>
@@ -93731,7 +93731,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Why the Gini value needs a caution, blank where nothing does; several are separated by "; ". consumption-based (not income): The survey measures household consumption, not income; consumption is spread more evenly, so the Gini is lower than an income Gini of the same country would be. | break in time series: new PIP survey-comparability spell: The World Bank marks this survey as not comparable with the country's earlier ones: a change from the previous value may reflect the change of survey. | OECD equivalised disposable income (not World Bank): New Zealand, which the World Bank does not cover: OECD Gini of equivalised household disposable income, a different concept from the World Bank's income per person.</t>
+          <t>Why the Gini value needs a caution, blank where nothing does; several are separated by "; ". consumption-based (not income): The survey measures household consumption, not income: a different welfare concept. Consumption Ginis are often, but not always, lower than income Ginis, so neither the direction nor the size of the difference can be assumed. | break in time series: new PIP survey-comparability spell: The World Bank marks this survey as not comparable with the country's earlier ones: a change from the previous value may reflect the change of survey. | OECD equivalised disposable income (not World Bank): New Zealand, which the World Bank does not cover: OECD Gini of equivalised household disposable income, a different concept from the World Bank's income per person.</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr"/>
@@ -94325,7 +94325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -94337,7 +94337,7 @@
     <col width="72" customWidth="1" min="7" max="7"/>
     <col width="69" customWidth="1" min="8" max="8"/>
     <col width="72" customWidth="1" min="9" max="9"/>
-    <col width="48" customWidth="1" min="10" max="10"/>
+    <col width="72" customWidth="1" min="10" max="10"/>
     <col width="72" customWidth="1" min="11" max="11"/>
     <col width="72" customWidth="1" min="12" max="12"/>
     <col width="72" customWidth="1" min="13" max="13"/>
@@ -97317,6 +97317,110 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>documentation corrected</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Gini index: what the consumption-based flag means (GitHub issue #33, Gini audit finding G01)</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>吉尼指數：消費基礎旗標之意涵（GitHub issue #33，吉尼指數稽核發現 G01）</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>consumption-based Ginis "are lower than an income Gini of the same country would be"</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>消費基礎吉尼值「低於同國以所得計算之吉尼值」</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>a different welfare concept: often, but not always, lower; direction and size cannot be assumed</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>屬不同之福利概念：常較低但並非必然；差異方向與大小均無法預設</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Values and flags unchanged. The README, known issues, comparability text, analysis notes and the clean workbook said a consumption Gini is always lower than the income Gini of the same country. The World Bank says inequality often is higher on income (PIP methodology, chapter 2, now archived), and where its survey table has both measures for a country-year in the panel's scope the consumption Gini is higher in 24 of 48 (data/gini_income_consumption_pairs.csv). The texts now say often, not always, in English and Chinese.</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>數值與旗標不變。README、已知問題、可比性說明、分析說明與精簡活頁簿原稱消費吉尼值必然低於同國之所得吉尼值。世界銀行指出以所得衡量之不平等「常」較高（PIP 方法說明第 2 章，現已存檔）；在 panel 範圍內世界銀行調查表同時列有兩種衡量之國家年度中，48 個之中有 24 個消費吉尼值較高（data/gini_income_consumption_pairs.csv）。中英文說明現改為「常較低，但並非必然」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>documentation corrected</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Evidence pages and file descriptions: checks against a copy of the same series</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>佐證頁與檔案說明：與同一序列轉載值之核對</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>"Independent check" for the World Bank's copy of the ILO series, Our World in Data's copy of V-Dem, the World Bank's PIP survey table and WHO's API</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>世界銀行轉載之國際勞工組織序列、Our World in Data 轉載之 V-Dem、世界銀行 PIP 調查表與 WHO API 均標為「獨立核對」</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>"Cross-check", naming what each is (a copy, the source of WDI's values, the original publisher)</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>改標為「交叉核對」，並說明其性質（轉載、WDI 數值之來源、原始發布機構）</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Values unchanged. A copy of the same series confirms that the archive read the publisher's file correctly, not that the values are right; the Gini audit of 2026-10-29 made the point for the World Bank's PIP table, and the same label stood on the other copies. The labels and the descriptions in data/api_snapshots.csv now say what each check is.</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>數值不變。同一序列之轉載值僅能確認存檔正確讀取發布機構之檔案，無法證明數值本身正確；2026-10-29 之吉尼指數稽核就世界銀行 PIP 調查表指出此點，其他轉載亦用同一標示。標示與 data/api_snapshots.csv 之說明現已載明每項核對之性質。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/CLEAN_country_year_panel_2010-2022.xlsx
+++ b/data/CLEAN_country_year_panel_2010-2022.xlsx
@@ -97323,6 +97323,16 @@
           <t>2026-10-29</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>22:48</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>bfc542f</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
           <t>documentation corrected</t>
@@ -97373,6 +97383,16 @@
       <c r="A46" t="inlineStr">
         <is>
           <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>22:48</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>bfc542f</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
